--- a/data/min_max_investment_analysis.xlsx
+++ b/data/min_max_investment_analysis.xlsx
@@ -505,37 +505,37 @@
         <v>9.202299999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>4.7908</v>
+        <v>4.790752380952381</v>
       </c>
       <c r="D2" t="n">
-        <v>2.96</v>
+        <v>2.962116107701873</v>
       </c>
       <c r="E2" t="n">
-        <v>10296</v>
+        <v>10296.21161077019</v>
       </c>
       <c r="F2" t="n">
-        <v>296</v>
+        <v>296.2116107701877</v>
       </c>
       <c r="G2" t="n">
-        <v>2.96</v>
+        <v>2.962116107701877</v>
       </c>
       <c r="H2" t="n">
         <v>5.2024</v>
       </c>
       <c r="I2" t="n">
-        <v>4.3533</v>
+        <v>4.35332</v>
       </c>
       <c r="J2" t="n">
-        <v>-1.26</v>
+        <v>-1.259778735684935</v>
       </c>
       <c r="K2" t="n">
-        <v>9874</v>
+        <v>9874.022126431506</v>
       </c>
       <c r="L2" t="n">
-        <v>-126</v>
+        <v>-125.977873568494</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.26</v>
+        <v>-1.25977873568494</v>
       </c>
     </row>
     <row r="3">
@@ -548,37 +548,37 @@
         <v>9.202299999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>4.5977</v>
+        <v>4.597733333333333</v>
       </c>
       <c r="D3" t="n">
-        <v>3.09</v>
+        <v>3.093444767194953</v>
       </c>
       <c r="E3" t="n">
-        <v>10309</v>
+        <v>10309.3444767195</v>
       </c>
       <c r="F3" t="n">
-        <v>309</v>
+        <v>309.344476719496</v>
       </c>
       <c r="G3" t="n">
-        <v>3.09</v>
+        <v>3.09344476719496</v>
       </c>
       <c r="H3" t="n">
         <v>5.2024</v>
       </c>
       <c r="I3" t="n">
-        <v>4.28</v>
+        <v>4.27999</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.53</v>
+        <v>-0.5289089917073997</v>
       </c>
       <c r="K3" t="n">
-        <v>9947</v>
+        <v>9947.109100829261</v>
       </c>
       <c r="L3" t="n">
-        <v>-53</v>
+        <v>-52.89089917073943</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.53</v>
+        <v>-0.5289089917073944</v>
       </c>
     </row>
     <row r="4">
@@ -591,37 +591,37 @@
         <v>9.202299999999999</v>
       </c>
       <c r="C4" t="n">
-        <v>5.3353</v>
+        <v>5.33532380952381</v>
       </c>
       <c r="D4" t="n">
-        <v>2.71</v>
+        <v>2.70922008866199</v>
       </c>
       <c r="E4" t="n">
-        <v>10271</v>
+        <v>10270.9220088662</v>
       </c>
       <c r="F4" t="n">
-        <v>270.9999999999982</v>
+        <v>270.9220088661987</v>
       </c>
       <c r="G4" t="n">
-        <v>2.709999999999982</v>
+        <v>2.709220088661987</v>
       </c>
       <c r="H4" t="n">
         <v>5.2024</v>
       </c>
       <c r="I4" t="n">
-        <v>5.0006</v>
+        <v>5.000565</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.47</v>
+        <v>-0.465706253459619</v>
       </c>
       <c r="K4" t="n">
-        <v>9953</v>
+        <v>9953.429374654039</v>
       </c>
       <c r="L4" t="n">
-        <v>-47</v>
+        <v>-46.57062534596116</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.47</v>
+        <v>-0.4657062534596116</v>
       </c>
     </row>
     <row r="5">
@@ -634,37 +634,37 @@
         <v>9.202299999999999</v>
       </c>
       <c r="C5" t="n">
-        <v>4.3033</v>
+        <v>4.303347619047619</v>
       </c>
       <c r="D5" t="n">
-        <v>5.27</v>
+        <v>5.269086438132042</v>
       </c>
       <c r="E5" t="n">
-        <v>10527</v>
+        <v>10526.9086438132</v>
       </c>
       <c r="F5" t="n">
-        <v>527</v>
+        <v>526.9086438132035</v>
       </c>
       <c r="G5" t="n">
-        <v>5.27</v>
+        <v>5.269086438132035</v>
       </c>
       <c r="H5" t="n">
         <v>5.2024</v>
       </c>
       <c r="I5" t="n">
-        <v>3.9585</v>
+        <v>3.958525</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.31</v>
+        <v>-1.309448903029731</v>
       </c>
       <c r="K5" t="n">
-        <v>9869</v>
+        <v>9869.055109697027</v>
       </c>
       <c r="L5" t="n">
-        <v>-131</v>
+        <v>-130.9448903029734</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.31</v>
+        <v>-1.309448903029734</v>
       </c>
     </row>
     <row r="6">
@@ -677,37 +677,37 @@
         <v>9.202299999999999</v>
       </c>
       <c r="C6" t="n">
-        <v>2.7645</v>
+        <v>2.764457142857143</v>
       </c>
       <c r="D6" t="n">
-        <v>4.27</v>
+        <v>4.264948307924255</v>
       </c>
       <c r="E6" t="n">
-        <v>10427</v>
+        <v>10426.49483079243</v>
       </c>
       <c r="F6" t="n">
-        <v>427</v>
+        <v>426.494830792426</v>
       </c>
       <c r="G6" t="n">
-        <v>4.27</v>
+        <v>4.26494830792426</v>
       </c>
       <c r="H6" t="n">
         <v>3.2024</v>
       </c>
       <c r="I6" t="n">
-        <v>2.5975</v>
+        <v>2.597471428571429</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.77</v>
+        <v>-0.7720392277424382</v>
       </c>
       <c r="K6" t="n">
-        <v>9923</v>
+        <v>9922.796077225756</v>
       </c>
       <c r="L6" t="n">
-        <v>-77</v>
+        <v>-77.20392277424435</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.77</v>
+        <v>-0.7720392277424435</v>
       </c>
     </row>
     <row r="7">
@@ -720,37 +720,37 @@
         <v>10.2023</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1169</v>
+        <v>0.1169181818181818</v>
       </c>
       <c r="D7" t="n">
-        <v>0.26</v>
+        <v>0.3138510451797361</v>
       </c>
       <c r="E7" t="n">
-        <v>10026</v>
+        <v>10031.38510451797</v>
       </c>
       <c r="F7" t="n">
-        <v>26</v>
+        <v>31.38510451797447</v>
       </c>
       <c r="G7" t="n">
-        <v>0.26</v>
+        <v>0.3138510451797447</v>
       </c>
       <c r="H7" t="n">
         <v>6.2024</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0992</v>
+        <v>0.09918666666666667</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.3</v>
+        <v>-0.3249254681271463</v>
       </c>
       <c r="K7" t="n">
-        <v>9970</v>
+        <v>9967.507453187285</v>
       </c>
       <c r="L7" t="n">
-        <v>-30</v>
+        <v>-32.49254681271486</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3</v>
+        <v>-0.3249254681271486</v>
       </c>
     </row>
     <row r="8">
@@ -763,37 +763,37 @@
         <v>9.202299999999999</v>
       </c>
       <c r="C8" t="n">
-        <v>0.4013</v>
+        <v>0.4013190476190476</v>
       </c>
       <c r="D8" t="n">
-        <v>2.69</v>
+        <v>2.69764278208986</v>
       </c>
       <c r="E8" t="n">
-        <v>10269</v>
+        <v>10269.76427820899</v>
       </c>
       <c r="F8" t="n">
-        <v>269</v>
+        <v>269.7642782089861</v>
       </c>
       <c r="G8" t="n">
-        <v>2.69</v>
+        <v>2.697642782089861</v>
       </c>
       <c r="H8" t="n">
         <v>4.2024</v>
       </c>
       <c r="I8" t="n">
-        <v>0.3683</v>
+        <v>0.3683047619047619</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.45</v>
+        <v>-1.452525355486456</v>
       </c>
       <c r="K8" t="n">
-        <v>9855</v>
+        <v>9854.747464451355</v>
       </c>
       <c r="L8" t="n">
-        <v>-145</v>
+        <v>-145.252535548645</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.45</v>
+        <v>-1.45252535548645</v>
       </c>
     </row>
   </sheetData>
